--- a/ig/nriss-change-pr-template/StructureDefinition-fr-core-patient-birthdate-update-indicator.xlsx
+++ b/ig/nriss-change-pr-template/StructureDefinition-fr-core-patient-birthdate-update-indicator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-11T13:10:53+00:00</t>
+    <t>2023-12-11T13:11:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
